--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/sep-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/sep-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC sep-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC sep-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/sep-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/sep-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -623,7 +623,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>77.146.212-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>77.146.212-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>77.430.680-3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1429,7 +1453,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>599-334-CM25</t>
+          <t>721703-475-SE25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1468,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1478,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.980.230-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>AGENCIA DE CALIDAD DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,28 +1493,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>VICTORIA SpA</t>
+          <t>KLEINROCK SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.188.587-1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>77.146.212-K</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>255499.44</v>
+        <v>16916.56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>722-158-CM25</t>
+          <t>599-334-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,48 +1538,52 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.083.021-6</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>25422.25</v>
+        <v>255499.44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4127-29-CM25</t>
+          <t>722-158-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,37 +1598,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.975.700-9</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SOC DE INVESTIGACION Y DESARROLLO KBINNOVA LIMITADA</t>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.098.050-1</t>
+          <t>76.083.021-6</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1638,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>382158.49</v>
+        <v>25422.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>586-404-CM25</t>
+          <t>4127-29-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1637,27 +1669,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.975.700-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>SOC DE INVESTIGACION Y DESARROLLO KBINNOVA LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
+          <t>76.098.050-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1699,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>45751.4</v>
+        <v>382158.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>610-83-CM25</t>
+          <t>586-404-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1698,27 +1730,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.707.000-6</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Energía</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>RIALIS SPA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.348.639-7</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1760,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>29854.25</v>
+        <v>45751.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2981-1240-CM25</t>
+          <t>610-83-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,12 +1791,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.707.000-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>Comisión Nacional de Energía</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1806,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>EMTEC CHILE S.A.</t>
+          <t>RIALIS SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.058.349-9</t>
+          <t>76.348.639-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1821,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>67525.86</v>
+        <v>29854.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>957865-372-CM25</t>
+          <t>2981-1240-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,12 +1852,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.980.820-7</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DERECHOS HUMANOS</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1867,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>EMTEC CHILE S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.058.349-9</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1882,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>15913.53</v>
+        <v>67525.86</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>711841-549-CM25</t>
+          <t>957865-372-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,12 +1913,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.103.000-4</t>
+          <t>61.980.820-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+          <t>SUBSECRETARIA DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,28 +1928,32 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>16686.91</v>
+        <v>15913.53</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1398-2284-CM25</t>
+          <t>711841-549-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,48 +1973,52 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>60.103.000-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>36105.67</v>
+        <v>16686.91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2305-65-CM25</t>
+          <t>1398-2284-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1998,48 +2038,52 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.973.000-3</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>UNIDAD DE ANALISIS FINANCIERO</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PAULA ALEJANDRA QUITRAL HERRERA, SERVICIOS INFORMATICOS, EMPRESA INDIV</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.092.019-3</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>21040.31</v>
+        <v>36105.67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1375754-40-CM25</t>
+          <t>2305-65-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2098,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2108,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.981.260-3</t>
+          <t>61.973.000-3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS PARQUES</t>
+          <t>UNIDAD DE ANALISIS FINANCIERO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,28 +2123,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CONSULTORA, CHERRIE PIZARRO SANTOS EMPRESA INDIVIDUAL DE RESPONSABILID</t>
+          <t>PAULA ALEJANDRA QUITRAL HERRERA, SERVICIOS INFORMATICOS, EMPRESA INDIV</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.522.707-0</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>76.092.019-3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>20061.65</v>
+        <v>21040.31</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4467-6-CM25</t>
+          <t>1375754-40-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2125,12 +2173,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>61.981.260-3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS PARQUES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2188,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>KLEINROCK SPA</t>
+          <t>CONSULTORA, CHERRIE PIZARRO SANTOS EMPRESA INDIVIDUAL DE RESPONSABILID</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.146.212-K</t>
+          <t>76.522.707-0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,7 +2203,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>57029.73</v>
+        <v>20061.65</v>
       </c>
     </row>
     <row r="29">
@@ -2209,7 +2257,11 @@
           <t>76.260.080-3</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2222,7 +2274,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>609-379-CM25</t>
+          <t>4467-6-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2247,12 +2299,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,22 +2314,26 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>BLUE COMPANY S A</t>
+          <t>KLEINROCK SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.981.410-2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>77.146.212-K</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>20897.68</v>
+        <v>57029.73</v>
       </c>
     </row>
     <row r="31">
@@ -2344,7 +2400,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2580-1108-CM25</t>
+          <t>609-379-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2415,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2425,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2440,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>BLUE COMPANY S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
+          <t>96.981.410-2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2455,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>365454.67</v>
+        <v>20897.68</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4127-196-CM25</t>
+          <t>2580-1108-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2476,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2486,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.975.700-9</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,28 +2501,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>510212.77</v>
+        <v>365454.67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>622844-39-CM25</t>
+          <t>4127-196-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2491,12 +2551,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.975.700-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,28 +2566,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.198.095-5</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>96.777.670-k</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>29902.55</v>
+        <v>510212.77</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>45-325-CM25</t>
+          <t>622844-39-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2552,12 +2616,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2631,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Fernando Marcelo</t>
+          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.811.563-K</t>
+          <t>76.198.095-5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2646,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>41786.86</v>
+        <v>29902.55</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4467-5-CM25</t>
+          <t>45-325-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2608,17 +2672,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,28 +2692,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>KLEINROCK SPA</t>
+          <t>Fernando Marcelo</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.146.212-K</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>76.811.563-K</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>17759.7</v>
+        <v>41786.86</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1602-137-CM25</t>
+          <t>4467-5-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2669,17 +2737,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2697,20 +2765,24 @@
           <t>77.146.212-K</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>29728.19</v>
+        <v>17759.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2216-604-CM25</t>
+          <t>1602-137-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,22 +2797,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MOP Dirección General de Concesiones</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,28 +2822,32 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>KLEINROCK SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>77.146.212-K</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>142222.77</v>
+        <v>29728.19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4467-7-CM25</t>
+          <t>593951-642-SE25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,22 +2862,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,28 +2887,32 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>77.842.230-1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>24325.88</v>
+        <v>41168.14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1019-472-CM25</t>
+          <t>2216-604-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2927,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2862,7 +2942,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MOP Dirección General de Concesiones</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2952,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Geosolve Cia Ltda</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.562.690-0</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2967,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>32267.16</v>
+        <v>142222.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3471-2612-CM25</t>
+          <t>4467-7-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,22 +2988,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.505.723-3</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,28 +3013,32 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>35356.15</v>
+        <v>24325.88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14-508-CM25</t>
+          <t>1019-472-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,22 +3053,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +3078,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
+          <t>Geosolve Cia Ltda</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.842.230-1</t>
+          <t>76.562.690-0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3093,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>16414.2</v>
+        <v>32267.16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>756-392-CM25</t>
+          <t>14-508-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3040,12 +3124,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.701.000-5</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,28 +3139,32 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>AQUANTA INGENIERIA COMPUTACIONAL SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>77.842.230-1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>16501.98</v>
+        <v>16414.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>761-611-CM25</t>
+          <t>756-392-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3179,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3189,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.515.000-4</t>
+          <t>60.701.000-5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,28 +3204,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>76.891.821-k</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>19499.99</v>
+        <v>16501.98</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>895072-167-CM25</t>
+          <t>3471-2612-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3244,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3254,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.980.540-2</t>
+          <t>60.505.723-3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION PARVULARIA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3269,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>77.205.722-9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3284,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>20057.55</v>
+        <v>35356.15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>586-370-CM25</t>
+          <t>761-611-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3305,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,27 +3315,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>60.515.000-4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DE DESARROLLO REGIONAL Y ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CLOUDHESIVE CHILE SPA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.014.934-7</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3345,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>151581.75</v>
+        <v>19499.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>586-402-CM25</t>
+          <t>895072-167-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3366,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,43 +3376,47 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>61.980.540-2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DE EDUCACION PARVULARIA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.011.398-0</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>76.304.354-1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>193181.61</v>
+        <v>20057.55</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1469-2770-CM25</t>
+          <t>586-370-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3340,32 +3436,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>CLOUDHESIVE CHILE SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>77.014.934-7</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3471,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>19842.27</v>
+        <v>151581.75</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>875-128-CM25</t>
+          <t>586-402-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,7 +3492,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,27 +3502,27 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.720.000-9</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SILOCYDATA SPA</t>
+          <t>CONSULTORIA Y DESARROLLO DE SOFTWARE ARKHOTECH SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.185.932-1</t>
+          <t>76.011.398-0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3532,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>7120.81</v>
+        <v>193181.61</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5514-52-CM25</t>
+          <t>1469-2770-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3553,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,43 +3563,47 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>76.232.892-5</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>60448.32</v>
+        <v>19842.27</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1375756-79-CM25</t>
+          <t>875-128-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3528,43 +3628,47 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.981.270-0</t>
+          <t>60.720.000-9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PETORCA</t>
+          <t>AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CONSULTORA, CHERRIE PIZARRO SANTOS EMPRESA INDIVIDUAL DE RESPONSABILID</t>
+          <t>SILOCYDATA SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.522.707-0</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>77.185.932-1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>20590.82</v>
+        <v>7120.81</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3637-281-CM25</t>
+          <t>5514-52-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3584,32 +3688,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.251.500-5</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMÁTICOS EN NUBE SPA</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.730.436-4</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3723,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>6857.41</v>
+        <v>60448.32</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1602-140-CM25</t>
+          <t>1375756-79-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3744,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,27 +3754,27 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.981.270-0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PETORCA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>VAB Ingeniería de Software Limitada</t>
+          <t>CONSULTORA, CHERRIE PIZARRO SANTOS EMPRESA INDIVIDUAL DE RESPONSABILID</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.090.261-6</t>
+          <t>76.522.707-0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3784,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>20181.78</v>
+        <v>20590.82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1233619-1034-CM25</t>
+          <t>3637-281-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3805,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,43 +3815,47 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>69.251.500-5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Diseño y Desarrollo Visualmente SpA</t>
+          <t>SERVICIOS INFORMÁTICOS EN NUBE SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.046.871-1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>77.730.436-4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>13639.82</v>
+        <v>6857.41</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>948354-1232-CM25</t>
+          <t>1602-140-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3767,17 +3875,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.513.003-6</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3895,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SALUD GESTIONADA SPA</t>
+          <t>VAB Ingeniería de Software Limitada</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.144.274-9</t>
+          <t>76.090.261-6</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,7 +3910,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>78443.97</v>
+        <v>20181.78</v>
       </c>
     </row>
     <row r="56">
@@ -3917,7 +4025,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3925,6 +4037,197 @@
       </c>
       <c r="M57" s="2" t="n">
         <v>110147.94</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1233619-1034-CM25</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>61.980.930-0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Diseño y Desarrollo Visualmente SpA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>76.046.871-1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>13639.82</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>948354-1232-CM25</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>61.513.003-6</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>SALUD GESTIONADA SPA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>77.144.274-9</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>78443.97</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1057547-33585-SE25</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>45973.97</v>
       </c>
     </row>
   </sheetData>
